--- a/data/trans_dic/P19F$mañana-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19F$mañana-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la mañana</t>
+          <t>Población que, al menos, se cepilla los dientes por la mañana (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,0; 62,8</t>
+          <t>46,98; 63,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,44; 70,73</t>
+          <t>55,0; 69,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,58; 64,95</t>
+          <t>53,32; 64,05</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,96; 51,48</t>
+          <t>38,68; 52,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,83; 52,16</t>
+          <t>38,28; 50,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,09; 49,31</t>
+          <t>40,77; 50,09</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,41; 70,52</t>
+          <t>53,74; 70,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,44; 78,66</t>
+          <t>59,57; 77,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,07; 70,59</t>
+          <t>59,11; 71,04</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,31; 53,65</t>
+          <t>38,69; 53,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,12; 64,31</t>
+          <t>50,54; 64,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,83; 56,8</t>
+          <t>47,41; 57,14</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,51</t>
+          <t>3,8; 12,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,87; 21,11</t>
+          <t>9,99; 21,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 15,33</t>
+          <t>7,84; 15,1</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,89; 36,91</t>
+          <t>21,73; 36,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,61; 31,43</t>
+          <t>18,64; 31,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,24; 32,31</t>
+          <t>21,56; 31,33</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,93; 37,68</t>
+          <t>27,71; 37,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,89; 43,41</t>
+          <t>32,74; 43,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,56; 38,94</t>
+          <t>31,65; 39,17</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,23; 52,95</t>
+          <t>41,4; 52,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45,7; 57,69</t>
+          <t>46,19; 57,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,81; 53,71</t>
+          <t>45,22; 53,25</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38,66; 43,19</t>
+          <t>38,16; 43,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42,51; 47,35</t>
+          <t>42,49; 47,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41,32; 44,73</t>
+          <t>41,2; 44,52</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la mañana</t>
+          <t>Población que, al menos, se cepilla los dientes por la mañana (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84254; 112577</t>
+          <t>84209; 113821</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88119; 114504</t>
+          <t>89030; 113206</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>182766; 221565</t>
+          <t>181874; 218508</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98700; 130402</t>
+          <t>97970; 131798</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91980; 123574</t>
+          <t>90693; 120440</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>196519; 241697</t>
+          <t>199856; 245521</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>74910; 97089</t>
+          <t>73986; 96540</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59014; 76797</t>
+          <t>58164; 75430</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139006; 166119</t>
+          <t>139088; 167161</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82145; 112105</t>
+          <t>80850; 111636</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115665; 145501</t>
+          <t>114341; 145195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>203818; 247186</t>
+          <t>206319; 248670</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5128; 18205</t>
+          <t>5535; 17921</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14588; 31217</t>
+          <t>14773; 31884</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23329; 44966</t>
+          <t>23003; 44310</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32201; 54298</t>
+          <t>31963; 53813</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33120; 55939</t>
+          <t>33170; 56281</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72295; 105029</t>
+          <t>70070; 101831</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>106465; 143625</t>
+          <t>105603; 144061</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118488; 156398</t>
+          <t>117945; 157464</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>233997; 288686</t>
+          <t>234658; 290371</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>134348; 172523</t>
+          <t>134912; 171231</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>152549; 192592</t>
+          <t>154201; 191241</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>302210; 354294</t>
+          <t>298298; 351270</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>687665; 768305</t>
+          <t>678823; 766106</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>740774; 825126</t>
+          <t>740350; 828265</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1455044; 1575069</t>
+          <t>1450680; 1567574</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$mañana-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19F$mañana-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,98; 63,5</t>
+          <t>48,51; 63,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,0; 69,93</t>
+          <t>55,67; 70,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,32; 64,05</t>
+          <t>53,63; 64,31</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,68; 52,03</t>
+          <t>39,53; 51,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,28; 50,84</t>
+          <t>38,7; 51,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,77; 50,09</t>
+          <t>40,67; 49,64</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,74; 70,12</t>
+          <t>54,58; 70,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,57; 77,26</t>
+          <t>60,18; 77,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,11; 71,04</t>
+          <t>58,15; 70,83</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,69; 53,43</t>
+          <t>39,2; 52,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,54; 64,18</t>
+          <t>50,51; 64,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,41; 57,14</t>
+          <t>46,81; 57,09</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 12,32</t>
+          <t>3,62; 12,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,99; 21,56</t>
+          <t>10,33; 22,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,1</t>
+          <t>7,71; 15,19</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,73; 36,58</t>
+          <t>22,23; 37,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,64; 31,63</t>
+          <t>19,15; 32,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,56; 31,33</t>
+          <t>22,1; 31,84</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,71; 37,8</t>
+          <t>27,36; 37,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,74; 43,71</t>
+          <t>33,28; 43,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,65; 39,17</t>
+          <t>31,47; 38,85</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,4; 52,55</t>
+          <t>41,53; 52,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46,19; 57,29</t>
+          <t>45,53; 57,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,22; 53,25</t>
+          <t>45,6; 53,81</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38,16; 43,07</t>
+          <t>38,71; 43,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42,49; 47,53</t>
+          <t>42,57; 47,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41,2; 44,52</t>
+          <t>41,2; 44,45</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84209; 113821</t>
+          <t>86961; 113999</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89030; 113206</t>
+          <t>90120; 113582</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>181874; 218508</t>
+          <t>182932; 219387</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97970; 131798</t>
+          <t>100143; 130084</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90693; 120440</t>
+          <t>91676; 122854</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>199856; 245521</t>
+          <t>199343; 243328</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>73986; 96540</t>
+          <t>75150; 96819</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58164; 75430</t>
+          <t>58757; 75787</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139088; 167161</t>
+          <t>136843; 166678</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>80850; 111636</t>
+          <t>81909; 110302</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>114341; 145195</t>
+          <t>114270; 145998</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>206319; 248670</t>
+          <t>203718; 248452</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5535; 17921</t>
+          <t>5270; 17718</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14773; 31884</t>
+          <t>15271; 32808</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23003; 44310</t>
+          <t>22606; 44566</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31963; 53813</t>
+          <t>32701; 54811</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33170; 56281</t>
+          <t>34078; 57060</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70070; 101831</t>
+          <t>71840; 103507</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>105603; 144061</t>
+          <t>104271; 143959</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>117945; 157464</t>
+          <t>119894; 157588</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>234658; 290371</t>
+          <t>233309; 288056</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>134912; 171231</t>
+          <t>135337; 171324</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>154201; 191241</t>
+          <t>151993; 191759</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>298298; 351270</t>
+          <t>300773; 354939</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>678823; 766106</t>
+          <t>688651; 772357</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>740350; 828265</t>
+          <t>741817; 827572</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1450680; 1567574</t>
+          <t>1450668; 1565117</t>
         </is>
       </c>
     </row>
